--- a/Excel/Vertical/perbandingan_Panjang Jalur Real.xlsx
+++ b/Excel/Vertical/perbandingan_Panjang Jalur Real.xlsx
@@ -453,10 +453,10 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>23.60406572566844</v>
+        <v>23.47851092925225</v>
       </c>
       <c r="F2">
-        <v>0.02228758492822003</v>
+        <v>0.02748823487787802</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -476,10 +476,10 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>48.09665262636237</v>
+        <v>48.67111123675181</v>
       </c>
       <c r="F3">
-        <v>0.03223100643011231</v>
+        <v>0.02067213068998591</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -499,10 +499,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>97.22092897251733</v>
+        <v>98.69177760110119</v>
       </c>
       <c r="F4">
-        <v>0.03561365015469115</v>
+        <v>0.02102351657865889</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -522,10 +522,10 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>195.5180908545122</v>
+        <v>198.769822173293</v>
       </c>
       <c r="F5">
-        <v>0.03703021925738864</v>
+        <v>0.02101472431574518</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -545,13 +545,13 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>24.83719391510835</v>
+        <v>25.71936168599622</v>
       </c>
       <c r="F6">
-        <v>0.02813998453999569</v>
+        <v>-0.006378551909159417</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -568,13 +568,13 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>51.45450616521079</v>
+        <v>52.62700551746683</v>
       </c>
       <c r="F7">
-        <v>0.0047192610290541</v>
+        <v>-0.01796030794804262</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -591,13 +591,13 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>103.46142082518</v>
+        <v>105.9675221282317</v>
       </c>
       <c r="F8">
-        <v>0.005013670072657328</v>
+        <v>-0.01908745397978448</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -614,13 +614,13 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>207.7489479300626</v>
+        <v>212.7549252358647</v>
       </c>
       <c r="F9">
-        <v>0.003847257858033336</v>
+        <v>-0.02015631987346001</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -637,13 +637,13 @@
         <v>9</v>
       </c>
       <c r="E10">
-        <v>26.07496472499763</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="F10">
-        <v>-0.0300728842651958</v>
+        <v>0.02111254282008313</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -660,10 +660,10 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>53.44654890763028</v>
+        <v>53.34219364008838</v>
       </c>
       <c r="F11">
-        <v>-0.02699604782095845</v>
+        <v>-0.02499082111268117</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -683,10 +683,10 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>106.8203763569287</v>
+        <v>107.9564652188189</v>
       </c>
       <c r="F12">
-        <v>-0.01253965251627817</v>
+        <v>-0.02330852509169579</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -706,10 +706,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>214.3213788747858</v>
+        <v>216.4987168752647</v>
       </c>
       <c r="F13">
-        <v>-0.009002511567449597</v>
+        <v>-0.01925318988311117</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -729,10 +729,10 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>22.62089099732862</v>
+        <v>22.93245190266634</v>
       </c>
       <c r="F14">
-        <v>0.03971150968195278</v>
+        <v>0.02648531308942171</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -752,10 +752,10 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>46.75225471703789</v>
+        <v>47.27911736770578</v>
       </c>
       <c r="F15">
-        <v>0.03657057799053214</v>
+        <v>0.02571345501146957</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -775,10 +775,10 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>94.9009341377288</v>
+        <v>95.97244829778465</v>
       </c>
       <c r="F16">
-        <v>0.03622600172453791</v>
+        <v>0.02534415429459522</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -798,10 +798,10 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>197.7247416993117</v>
+        <v>193.3591101579424</v>
       </c>
       <c r="F17">
-        <v>0.003153747499426723</v>
+        <v>0.02516345354031427</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -821,13 +821,13 @@
         <v>11</v>
       </c>
       <c r="E18">
-        <v>23.85486567281982</v>
+        <v>22.84376684661083</v>
       </c>
       <c r="F18">
-        <v>-0.03849722508001274</v>
+        <v>0.005519930149500376</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -844,13 +844,13 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>47.71474284512288</v>
+        <v>46.69946093319749</v>
       </c>
       <c r="F19">
-        <v>-0.007589509291554949</v>
+        <v>0.01385014106452056</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -867,10 +867,10 @@
         <v>11</v>
       </c>
       <c r="E20">
-        <v>95.50992475463946</v>
+        <v>94.48572750867693</v>
       </c>
       <c r="F20">
-        <v>0.006397582516181568</v>
+        <v>0.01705244233502151</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -890,10 +890,10 @@
         <v>11</v>
       </c>
       <c r="E21">
-        <v>192.2919197484023</v>
+        <v>190.0974453381104</v>
       </c>
       <c r="F21">
-        <v>0.007084833514831893</v>
+        <v>0.01841618288870773</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>

--- a/Excel/Vertical/perbandingan_Panjang Jalur Real.xlsx
+++ b/Excel/Vertical/perbandingan_Panjang Jalur Real.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="15">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Tetap</t>
+  </si>
+  <si>
+    <t>Naik</t>
+  </si>
+  <si>
+    <t>Turun</t>
   </si>
 </sst>
 </file>
@@ -449,6 +455,12 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>24.14213562373095</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
@@ -466,6 +478,12 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
+      <c r="E3">
+        <v>49.698484809835</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3" t="s">
         <v>12</v>
       </c>
@@ -483,6 +501,12 @@
       <c r="D4" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>100.8111831820431</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
@@ -500,6 +524,12 @@
       <c r="D5" t="s">
         <v>3</v>
       </c>
+      <c r="E5">
+        <v>203.0365799264593</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
@@ -517,8 +547,14 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
+      <c r="E6">
+        <v>24.97056274847714</v>
+      </c>
+      <c r="F6">
+        <v>0.02292136616858504</v>
+      </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -534,8 +570,14 @@
       <c r="D7" t="s">
         <v>8</v>
       </c>
+      <c r="E7">
+        <v>50.52691193458118</v>
+      </c>
+      <c r="F7">
+        <v>0.02266164820039235</v>
+      </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -551,8 +593,14 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
+      <c r="E8">
+        <v>103.2964645562817</v>
+      </c>
+      <c r="F8">
+        <v>0.006600051076132551</v>
+      </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -568,8 +616,14 @@
       <c r="D9" t="s">
         <v>8</v>
       </c>
+      <c r="E9">
+        <v>208.0071426749365</v>
+      </c>
+      <c r="F9">
+        <v>0.002609218360479026</v>
+      </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -585,8 +639,14 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
+      <c r="E10">
+        <v>24.14213562373095</v>
+      </c>
+      <c r="F10">
+        <v>0.04628215084726901</v>
+      </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -602,8 +662,14 @@
       <c r="D11" t="s">
         <v>9</v>
       </c>
+      <c r="E11">
+        <v>49.698484809835</v>
+      </c>
+      <c r="F11">
+        <v>0.04502444918190493</v>
+      </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -619,8 +685,14 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
+      <c r="E12">
+        <v>100.8111831820431</v>
+      </c>
+      <c r="F12">
+        <v>0.0444208879415743</v>
+      </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -636,8 +708,14 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13">
+        <v>203.0365799264593</v>
+      </c>
+      <c r="F13">
+        <v>0.04412513505919654</v>
+      </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -653,8 +731,14 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
+      <c r="E14">
+        <v>24.14213562373095</v>
+      </c>
+      <c r="F14">
+        <v>-0.02486745433254392</v>
+      </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -670,8 +754,14 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
+      <c r="E15">
+        <v>49.69848480983499</v>
+      </c>
+      <c r="F15">
+        <v>-0.02414274530456828</v>
+      </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -687,8 +777,14 @@
       <c r="D16" t="s">
         <v>10</v>
       </c>
+      <c r="E16">
+        <v>100.8111831820431</v>
+      </c>
+      <c r="F16">
+        <v>-0.02379600336948742</v>
+      </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -704,8 +800,14 @@
       <c r="D17" t="s">
         <v>10</v>
       </c>
+      <c r="E17">
+        <v>203.0365799264593</v>
+      </c>
+      <c r="F17">
+        <v>-0.02362634074402557</v>
+      </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -721,8 +823,14 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18">
+        <v>23.09901951359279</v>
+      </c>
+      <c r="F18">
+        <v>-0.005592234135585857</v>
+      </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -738,8 +846,14 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19">
+        <v>46.86645192953345</v>
+      </c>
+      <c r="F19">
+        <v>0.01032380169808195</v>
+      </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -755,8 +869,14 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20">
+        <v>95.40233038888984</v>
+      </c>
+      <c r="F20">
+        <v>0.007516900976447314</v>
+      </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -772,8 +892,14 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21">
+        <v>191.4295326143042</v>
+      </c>
+      <c r="F21">
+        <v>0.01153784051558392</v>
+      </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/perbandingan_Panjang Jalur Real.xlsx
+++ b/Excel/Vertical/perbandingan_Panjang Jalur Real.xlsx
@@ -594,10 +594,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>103.2964645562817</v>
+        <v>102.4680374315355</v>
       </c>
       <c r="F8">
-        <v>0.006600051076132551</v>
+        <v>0.01456701748631037</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -617,10 +617,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>208.0071426749365</v>
+        <v>206.350288425444</v>
       </c>
       <c r="F9">
-        <v>0.002609218360479026</v>
+        <v>0.01055380686697356</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -824,10 +824,10 @@
         <v>11</v>
       </c>
       <c r="E18">
-        <v>23.09901951359279</v>
+        <v>23.12310562561766</v>
       </c>
       <c r="F18">
-        <v>-0.005592234135585857</v>
+        <v>-0.006640798434537064</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
@@ -847,10 +847,10 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>46.86645192953345</v>
+        <v>47.00870142385959</v>
       </c>
       <c r="F19">
-        <v>0.01032380169808195</v>
+        <v>0.007319927221585599</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -870,10 +870,10 @@
         <v>11</v>
       </c>
       <c r="E20">
-        <v>95.40233038888984</v>
+        <v>95.48180327461259</v>
       </c>
       <c r="F20">
-        <v>0.007516900976447314</v>
+        <v>0.006690134003471502</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
